--- a/Results/03_UVC_CPD_percentage_pvals_origin.xlsx
+++ b/Results/03_UVC_CPD_percentage_pvals_origin.xlsx
@@ -1,118 +1,109 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Aktuell\Eigene Dateien\Eigene Dateien_Marc\R\Github\EKB\BFS_UVC\Results\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12030"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="29">
-  <si>
-    <t>Location</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Dose</t>
-  </si>
-  <si>
-    <t>.y.</t>
-  </si>
-  <si>
-    <t>group1</t>
-  </si>
-  <si>
-    <t>group2</t>
-  </si>
-  <si>
-    <t>n1</t>
-  </si>
-  <si>
-    <t>n2</t>
-  </si>
-  <si>
-    <t>statistic</t>
-  </si>
-  <si>
-    <t>p</t>
-  </si>
-  <si>
-    <t>effect</t>
-  </si>
-  <si>
-    <t>p.adj</t>
-  </si>
-  <si>
-    <t>p.adj.signif</t>
-  </si>
-  <si>
-    <t>Basal</t>
-  </si>
-  <si>
-    <t>254nm</t>
-  </si>
-  <si>
-    <t>0 J/m²</t>
-  </si>
-  <si>
-    <t>Count_perc</t>
-  </si>
-  <si>
-    <t>Old_skin</t>
-  </si>
-  <si>
-    <t>Young_skin</t>
-  </si>
-  <si>
-    <t>Origin</t>
-  </si>
-  <si>
-    <t>ns</t>
-  </si>
-  <si>
-    <t>Suprabasal</t>
-  </si>
-  <si>
-    <t>222nm</t>
-  </si>
-  <si>
-    <t>30 J/m²</t>
-  </si>
-  <si>
-    <t>300 J/m²</t>
-  </si>
-  <si>
-    <t>1000 J/m²</t>
-  </si>
-  <si>
-    <t>**</t>
-  </si>
-  <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>2000 J/m²</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+  <si>
+    <t xml:space="preserve">Location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.y.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">group1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">group2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">statistic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">effect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.adj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.adj.signif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">222nm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 J/m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count_perc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Old_skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Young_skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Origin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">254nm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suprabasal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 J/m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300 J/m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1000 J/m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2000 J/m²</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -145,18 +136,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -438,11 +420,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -483,7 +465,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -502,37 +484,37 @@
       <c r="F2" t="s">
         <v>18</v>
       </c>
-      <c r="G2">
-        <v>11</v>
-      </c>
-      <c r="H2">
-        <v>10</v>
-      </c>
-      <c r="I2">
+      <c r="G2" t="n">
+        <v>11</v>
+      </c>
+      <c r="H2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I2" t="n">
         <v>41.5</v>
       </c>
-      <c r="J2">
-        <v>0.28599999999999998</v>
+      <c r="J2" t="n">
+        <v>0.286</v>
       </c>
       <c r="K2" t="s">
         <v>19</v>
       </c>
-      <c r="L2">
-        <v>0.36441935483871002</v>
+      <c r="L2" t="n">
+        <v>0.389333333333333</v>
       </c>
       <c r="M2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
         <v>16</v>
@@ -543,37 +525,37 @@
       <c r="F3" t="s">
         <v>18</v>
       </c>
-      <c r="G3">
-        <v>11</v>
-      </c>
-      <c r="H3">
-        <v>10</v>
-      </c>
-      <c r="I3">
-        <v>78.5</v>
-      </c>
-      <c r="J3">
-        <v>9.1600000000000001E-2</v>
+      <c r="G3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I3" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.286</v>
       </c>
       <c r="K3" t="s">
         <v>19</v>
       </c>
-      <c r="L3">
-        <v>0.12922142857142899</v>
+      <c r="L3" t="n">
+        <v>0.389333333333333</v>
       </c>
       <c r="M3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
         <v>16</v>
@@ -584,37 +566,37 @@
       <c r="F4" t="s">
         <v>18</v>
       </c>
-      <c r="G4">
-        <v>11</v>
-      </c>
-      <c r="H4">
-        <v>10</v>
-      </c>
-      <c r="I4">
-        <v>69.5</v>
-      </c>
-      <c r="J4">
-        <v>0.315</v>
+      <c r="G4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I4" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.566</v>
       </c>
       <c r="K4" t="s">
         <v>19</v>
       </c>
-      <c r="L4">
-        <v>0.38882812500000002</v>
+      <c r="L4" t="n">
+        <v>0.667589743589744</v>
       </c>
       <c r="M4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
         <v>16</v>
@@ -625,29 +607,29 @@
       <c r="F5" t="s">
         <v>18</v>
       </c>
-      <c r="G5">
-        <v>11</v>
-      </c>
-      <c r="H5">
-        <v>10</v>
-      </c>
-      <c r="I5">
-        <v>97</v>
-      </c>
-      <c r="J5">
-        <v>3.4199999999999999E-3</v>
+      <c r="G5" t="n">
+        <v>11</v>
+      </c>
+      <c r="H5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.566</v>
       </c>
       <c r="K5" t="s">
         <v>19</v>
       </c>
-      <c r="L5">
-        <v>6.5897560975609797E-3</v>
+      <c r="L5" t="n">
+        <v>0.667589743589744</v>
       </c>
       <c r="M5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -655,7 +637,7 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
         <v>16</v>
@@ -666,78 +648,78 @@
       <c r="F6" t="s">
         <v>18</v>
       </c>
-      <c r="G6">
-        <v>11</v>
-      </c>
-      <c r="H6">
-        <v>10</v>
-      </c>
-      <c r="I6">
-        <v>94.5</v>
-      </c>
-      <c r="J6">
-        <v>5.9300000000000004E-3</v>
+      <c r="G6" t="n">
+        <v>11</v>
+      </c>
+      <c r="H6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I6" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.696</v>
       </c>
       <c r="K6" t="s">
         <v>19</v>
       </c>
-      <c r="L6">
-        <v>1.0664999999999999E-2</v>
+      <c r="L6" t="n">
+        <v>0.757647058823529</v>
       </c>
       <c r="M6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
         <v>21</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" t="n">
+        <v>11</v>
+      </c>
+      <c r="H7" t="n">
+        <v>10</v>
+      </c>
+      <c r="I7" t="n">
+        <v>69</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="K7" t="s">
+        <v>19</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.431085714285714</v>
+      </c>
+      <c r="M7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
         <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7">
-        <v>11</v>
-      </c>
-      <c r="H7">
-        <v>10</v>
-      </c>
-      <c r="I7">
-        <v>47.5</v>
-      </c>
-      <c r="J7">
-        <v>0.56599999999999995</v>
-      </c>
-      <c r="K7" t="s">
-        <v>19</v>
-      </c>
-      <c r="L7">
-        <v>0.63645070422535199</v>
-      </c>
-      <c r="M7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>21</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
         <v>16</v>
@@ -748,34 +730,34 @@
       <c r="F8" t="s">
         <v>18</v>
       </c>
-      <c r="G8">
-        <v>11</v>
-      </c>
-      <c r="H8">
-        <v>10</v>
-      </c>
-      <c r="I8">
-        <v>47.5</v>
-      </c>
-      <c r="J8">
-        <v>0.56599999999999995</v>
+      <c r="G8" t="n">
+        <v>11</v>
+      </c>
+      <c r="H8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I8" t="n">
+        <v>39</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.273</v>
       </c>
       <c r="K8" t="s">
         <v>19</v>
       </c>
-      <c r="L8">
-        <v>0.63645070422535199</v>
+      <c r="L8" t="n">
+        <v>0.3864</v>
       </c>
       <c r="M8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
         <v>21</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
       </c>
       <c r="C9" t="s">
         <v>23</v>
@@ -789,37 +771,37 @@
       <c r="F9" t="s">
         <v>18</v>
       </c>
-      <c r="G9">
-        <v>11</v>
-      </c>
-      <c r="H9">
-        <v>10</v>
-      </c>
-      <c r="I9">
-        <v>46</v>
-      </c>
-      <c r="J9">
-        <v>0.54700000000000004</v>
+      <c r="G9" t="n">
+        <v>11</v>
+      </c>
+      <c r="H9" t="n">
+        <v>10</v>
+      </c>
+      <c r="I9" t="n">
+        <v>53</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.916</v>
       </c>
       <c r="K9" t="s">
         <v>19</v>
       </c>
-      <c r="L9">
-        <v>0.63548529411764698</v>
+      <c r="L9" t="n">
+        <v>0.957636363636364</v>
       </c>
       <c r="M9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s">
         <v>16</v>
@@ -830,34 +812,34 @@
       <c r="F10" t="s">
         <v>18</v>
       </c>
-      <c r="G10">
-        <v>11</v>
-      </c>
-      <c r="H10">
-        <v>10</v>
-      </c>
-      <c r="I10">
-        <v>62</v>
-      </c>
-      <c r="J10">
-        <v>0.64700000000000002</v>
+      <c r="G10" t="n">
+        <v>11</v>
+      </c>
+      <c r="H10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I10" t="n">
+        <v>52</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.834</v>
       </c>
       <c r="K10" t="s">
         <v>19</v>
       </c>
-      <c r="L10">
-        <v>0.70990277777777799</v>
+      <c r="L10" t="n">
+        <v>0.881931034482759</v>
       </c>
       <c r="M10" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
         <v>21</v>
-      </c>
-      <c r="B11" t="s">
-        <v>22</v>
       </c>
       <c r="C11" t="s">
         <v>24</v>
@@ -871,31 +853,31 @@
       <c r="F11" t="s">
         <v>18</v>
       </c>
-      <c r="G11">
-        <v>11</v>
-      </c>
-      <c r="H11">
-        <v>10</v>
-      </c>
-      <c r="I11">
-        <v>44.5</v>
-      </c>
-      <c r="J11">
-        <v>0.47699999999999998</v>
+      <c r="G11" t="n">
+        <v>11</v>
+      </c>
+      <c r="H11" t="n">
+        <v>10</v>
+      </c>
+      <c r="I11" t="n">
+        <v>62</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.641</v>
       </c>
       <c r="K11" t="s">
         <v>19</v>
       </c>
-      <c r="L11">
-        <v>0.56243283582089598</v>
+      <c r="L11" t="n">
+        <v>0.719170731707317</v>
       </c>
       <c r="M11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
@@ -912,37 +894,37 @@
       <c r="F12" t="s">
         <v>18</v>
       </c>
-      <c r="G12">
-        <v>11</v>
-      </c>
-      <c r="H12">
-        <v>10</v>
-      </c>
-      <c r="I12">
-        <v>70</v>
-      </c>
-      <c r="J12">
-        <v>0.314</v>
+      <c r="G12" t="n">
+        <v>11</v>
+      </c>
+      <c r="H12" t="n">
+        <v>10</v>
+      </c>
+      <c r="I12" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.227</v>
       </c>
       <c r="K12" t="s">
         <v>19</v>
       </c>
-      <c r="L12">
-        <v>0.38882812500000002</v>
+      <c r="L12" t="n">
+        <v>0.3263125</v>
       </c>
       <c r="M12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
         <v>21</v>
       </c>
-      <c r="B13" t="s">
-        <v>22</v>
-      </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D13" t="s">
         <v>16</v>
@@ -953,31 +935,31 @@
       <c r="F13" t="s">
         <v>18</v>
       </c>
-      <c r="G13">
-        <v>11</v>
-      </c>
-      <c r="H13">
-        <v>10</v>
-      </c>
-      <c r="I13">
-        <v>23.5</v>
-      </c>
-      <c r="J13">
-        <v>2.87E-2</v>
+      <c r="G13" t="n">
+        <v>11</v>
+      </c>
+      <c r="H13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I13" t="n">
+        <v>63</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.605</v>
       </c>
       <c r="K13" t="s">
         <v>19</v>
       </c>
-      <c r="L13">
-        <v>4.7235416666666703E-2</v>
+      <c r="L13" t="n">
+        <v>0.7038</v>
       </c>
       <c r="M13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
@@ -994,78 +976,78 @@
       <c r="F14" t="s">
         <v>18</v>
       </c>
-      <c r="G14">
-        <v>11</v>
-      </c>
-      <c r="H14">
-        <v>10</v>
-      </c>
-      <c r="I14">
-        <v>85</v>
-      </c>
-      <c r="J14">
-        <v>3.7699999999999997E-2</v>
+      <c r="G14" t="n">
+        <v>11</v>
+      </c>
+      <c r="H14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I14" t="n">
+        <v>46</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.453</v>
       </c>
       <c r="K14" t="s">
         <v>19</v>
       </c>
-      <c r="L14">
-        <v>5.9566000000000001E-2</v>
+      <c r="L14" t="n">
+        <v>0.548368421052632</v>
       </c>
       <c r="M14" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
         <v>21</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" t="n">
+        <v>11</v>
+      </c>
+      <c r="H15" t="n">
+        <v>10</v>
+      </c>
+      <c r="I15" t="n">
+        <v>86</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.0315</v>
+      </c>
+      <c r="K15" t="s">
+        <v>19</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.0658636363636364</v>
+      </c>
+      <c r="M15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
         <v>22</v>
-      </c>
-      <c r="C15" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" t="s">
-        <v>17</v>
-      </c>
-      <c r="F15" t="s">
-        <v>18</v>
-      </c>
-      <c r="G15">
-        <v>11</v>
-      </c>
-      <c r="H15">
-        <v>10</v>
-      </c>
-      <c r="I15">
-        <v>46.5</v>
-      </c>
-      <c r="J15">
-        <v>0.57199999999999995</v>
-      </c>
-      <c r="K15" t="s">
-        <v>19</v>
-      </c>
-      <c r="L15">
-        <v>0.63645070422535199</v>
-      </c>
-      <c r="M15" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>21</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D16" t="s">
         <v>16</v>
@@ -1076,33 +1058,235 @@
       <c r="F16" t="s">
         <v>18</v>
       </c>
-      <c r="G16">
-        <v>11</v>
-      </c>
-      <c r="H16">
-        <v>10</v>
-      </c>
-      <c r="I16">
+      <c r="G16" t="n">
+        <v>11</v>
+      </c>
+      <c r="H16" t="n">
+        <v>10</v>
+      </c>
+      <c r="I16" t="n">
+        <v>16</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.00662</v>
+      </c>
+      <c r="K16" t="s">
+        <v>19</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.01906125</v>
+      </c>
+      <c r="M16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H17" t="n">
+        <v>10</v>
+      </c>
+      <c r="I17" t="n">
+        <v>77</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K17" t="s">
+        <v>19</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.207793103448276</v>
+      </c>
+      <c r="M17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" t="n">
+        <v>11</v>
+      </c>
+      <c r="H18" t="n">
+        <v>10</v>
+      </c>
+      <c r="I18" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="K18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.472602739726027</v>
+      </c>
+      <c r="M18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" t="n">
+        <v>11</v>
+      </c>
+      <c r="H19" t="n">
+        <v>10</v>
+      </c>
+      <c r="I19" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.00595</v>
+      </c>
+      <c r="K19" t="s">
+        <v>19</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.0182466666666667</v>
+      </c>
+      <c r="M19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" t="n">
+        <v>11</v>
+      </c>
+      <c r="H20" t="n">
+        <v>10</v>
+      </c>
+      <c r="I20" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="K20" t="s">
+        <v>19</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.389333333333333</v>
+      </c>
+      <c r="M20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" t="n">
+        <v>11</v>
+      </c>
+      <c r="H21" t="n">
+        <v>10</v>
+      </c>
+      <c r="I21" t="n">
         <v>88</v>
       </c>
-      <c r="J16">
-        <v>1.9699999999999999E-2</v>
-      </c>
-      <c r="K16" t="s">
-        <v>19</v>
-      </c>
-      <c r="L16">
-        <v>3.3112765957446798E-2</v>
-      </c>
-      <c r="M16" t="s">
-        <v>27</v>
+      <c r="J21" t="n">
+        <v>0.0197</v>
+      </c>
+      <c r="K21" t="s">
+        <v>19</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.043152380952381</v>
+      </c>
+      <c r="M21" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:M16">
-    <sortCondition ref="A2"/>
-  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>